--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,43 +1195,43 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
@@ -1240,88 +1240,88 @@
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AU3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,143 +1191,143 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,143 +1585,143 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,92 +1191,92 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
         <v>1.8</v>
@@ -1288,46 +1288,46 @@
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
         <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY4" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,143 +1388,143 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD5" t="n">
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
@@ -1634,88 +1634,88 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,143 +994,143 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
         <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,92 +1388,92 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR5" t="n">
         <v>1.8</v>
@@ -1485,46 +1485,46 @@
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW5" t="n">
         <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
@@ -1634,88 +1634,88 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA6" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,143 +994,143 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,43 +1195,43 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
@@ -1240,88 +1240,88 @@
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA4" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,92 +1388,92 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI5" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AJ5" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO5" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
         <v>1.8</v>
@@ -1485,46 +1485,46 @@
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AW5" t="n">
         <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT6" t="n">
         <v>3</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,143 +994,143 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,92 +1388,92 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR5" t="n">
         <v>1.8</v>
@@ -1485,46 +1485,46 @@
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW5" t="n">
         <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD6" t="n">
         <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,143 +994,143 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,143 +1191,143 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AU3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,143 +1191,143 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA5" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,143 +1585,143 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL6" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM6" t="n">
         <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,143 +1191,143 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,43 +1392,43 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
         <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
         <v>1.3</v>
@@ -1437,88 +1437,88 @@
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH5" t="n">
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,143 +1585,143 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,143 +1191,143 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,143 +1585,143 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AU3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,92 +1388,92 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI5" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AJ5" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO5" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
         <v>1.8</v>
@@ -1485,46 +1485,46 @@
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AW5" t="n">
         <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,143 +1585,143 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT6" t="n">
         <v>3</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,88 +1195,88 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
         <v>1.8</v>
@@ -1288,46 +1288,46 @@
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
         <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY4" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD6" t="n">
         <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
         <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
@@ -1634,88 +1634,88 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA6" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
         <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,88 +1195,88 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI4" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AJ4" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO4" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
         <v>1.8</v>
@@ -1288,46 +1288,46 @@
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
         <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X3" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
         <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD5" t="n">
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,88 +998,88 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI3" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AJ3" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK3" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO3" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
         <v>1.8</v>
@@ -1091,46 +1091,46 @@
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
         <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
         <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN4" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA4" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,139 +1589,139 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,43 +998,43 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
         <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>1.3</v>
@@ -1043,88 +1043,88 @@
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
         <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT4" t="n">
         <v>3</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AU4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
         <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,139 +1589,139 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,43 +1195,43 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
@@ -1240,88 +1240,88 @@
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA4" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
@@ -1634,88 +1634,88 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,43 +1195,43 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
@@ -1240,88 +1240,88 @@
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA5" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD6" t="n">
         <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,88 +998,88 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR3" t="n">
         <v>1.8</v>
@@ -1091,46 +1091,46 @@
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
         <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY3" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD5" t="n">
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,88 +998,88 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI3" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AJ3" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK3" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO3" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
         <v>1.8</v>
@@ -1091,46 +1091,46 @@
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
         <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,43 +1195,43 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
@@ -1240,88 +1240,88 @@
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA4" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,88 +1392,88 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR5" t="n">
         <v>1.8</v>
@@ -1485,46 +1485,46 @@
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW5" t="n">
         <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
@@ -1634,88 +1634,88 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD6" t="n">
         <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -804,46 +804,46 @@
         <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.32</v>
+        <v>4.17</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="X2" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
@@ -852,82 +852,82 @@
         <v>2.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
         <v>1.43</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AT2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU2" t="n">
         <v>3.35</v>
       </c>
-      <c r="AU2" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AV2" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="BA2" t="n">
         <v>1.99</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>2.38</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>4.37</v>
+        <v>2.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
         <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,88 +998,88 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="X3" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AR3" t="n">
         <v>1.8</v>
@@ -1091,46 +1091,46 @@
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
         <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY3" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>4.37</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
         <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI5" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.91</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA5" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,43 +1589,43 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
@@ -1634,88 +1634,88 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -801,40 +801,40 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>3.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="S2" t="n">
-        <v>4.17</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X2" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AB2" t="n">
         <v>1.03</v>
@@ -843,7 +843,7 @@
         <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
@@ -852,34 +852,34 @@
         <v>2.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.47</v>
@@ -888,7 +888,7 @@
         <v>1.77</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AT2" t="n">
         <v>2.8</v>
@@ -897,37 +897,37 @@
         <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AY2" t="n">
         <v>1.37</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.99</v>
+        <v>1.49</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BC2" t="n">
         <v>1.66</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.79</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>5.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>5.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>2.9</v>
@@ -1210,25 +1210,25 @@
         <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="X4" t="n">
         <v>3.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
         <v>1.02</v>
@@ -1237,37 +1237,37 @@
         <v>1.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>4.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI4" t="n">
         <v>7.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AO4" t="n">
         <v>1.31</v>
@@ -1282,22 +1282,22 @@
         <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AY4" t="n">
         <v>1.3</v>
@@ -1306,22 +1306,22 @@
         <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>1.8</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S5" t="n">
         <v>3.45</v>
@@ -1437,10 +1437,10 @@
         <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>3.45</v>
@@ -1449,13 +1449,13 @@
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
         <v>1.94</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="R6" t="n">
-        <v>4.37</v>
+        <v>2.88</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="V6" t="n">
         <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AK6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW6" t="n">
         <v>2</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AX6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,25 +1795,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1822,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI8"/>
+  <dimension ref="A1:BI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>3.03</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.38</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="Z3" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="BE3" t="n">
         <v>1.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
         <v>3.9</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>4.2</v>
+        <v>5.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.6</v>
+        <v>5.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.14</v>
+        <v>3.52</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.23</v>
       </c>
-      <c r="AI4" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AN4" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.49</v>
+        <v>3.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BA4" t="n">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="BE4" t="n">
         <v>1.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1610,7 +1610,7 @@
         <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
         <v>2.85</v>
@@ -1688,7 +1688,7 @@
         <v>2.45</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AX6" t="n">
         <v>1.63</v>
@@ -1703,7 +1703,7 @@
         <v>1.94</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
         <v>2.16</v>
@@ -1725,400 +1725,6 @@
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="3" t="n">
-        <v>46105.875</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="3" t="n">
-        <v>46105.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="R3" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X3" t="n">
         <v>2.85</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
         <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.02</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.32</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA3" t="n">
         <v>1.94</v>
       </c>
-      <c r="AL3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="BB3" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
         <v>2.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>5.18</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.95</v>
+        <v>8.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG4" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.31</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.38</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z5" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
         <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
         <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>4.14</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.35</v>
+        <v>5.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.15</v>
+        <v>5.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>3.35</v>
+        <v>5.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="X3" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.15</v>
+        <v>5.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1079,52 +1079,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>2.31</v>
+        <v>3.03</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.38</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z4" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.45</v>
+        <v>4.14</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
         <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
         <v>1.02</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.32</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA5" t="n">
         <v>1.94</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="BB5" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
         <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>5.18</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
         <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
         <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.95</v>
+        <v>8.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG6" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="AS6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF6" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>5.18</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
         <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
         <v>2.8</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1231,10 +1231,10 @@
         <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AD4" t="n">
         <v>3.2</v>
@@ -1246,28 +1246,28 @@
         <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.14</v>
+        <v>3.55</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AM4" t="n">
         <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AO4" t="n">
         <v>1.31</v>
@@ -1288,7 +1288,7 @@
         <v>3.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.49</v>
+        <v>3.05</v>
       </c>
       <c r="AV4" t="n">
         <v>2.28</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>3.35</v>
+        <v>5.18</v>
       </c>
       <c r="V5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.35</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z5" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.15</v>
+        <v>5.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,52 +1473,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC5" t="n">
         <v>1.98</v>
       </c>
-      <c r="BA5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BD5" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="R6" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="V6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.38</v>
       </c>
-      <c r="W6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z6" t="n">
-        <v>8.9</v>
+        <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
         <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1.94</v>
       </c>
-      <c r="AM6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="U2" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -825,16 +825,16 @@
         <v>3.8</v>
       </c>
       <c r="X2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AB2" t="n">
         <v>1.03</v>
@@ -843,49 +843,49 @@
         <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL2" t="n">
         <v>2.7</v>
       </c>
       <c r="AM2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN2" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN2" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AS2" t="n">
         <v>1.93</v>
@@ -897,13 +897,13 @@
         <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AY2" t="n">
         <v>1.37</v>
@@ -912,22 +912,22 @@
         <v>2.43</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="R3" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="V3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.38</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z3" t="n">
-        <v>8.9</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA3" t="n">
         <v>1.94</v>
       </c>
-      <c r="AM3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>2.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>3.03</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AF4" t="n">
         <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>5.18</v>
+        <v>4.35</v>
       </c>
       <c r="V5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.38</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
         <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC5" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.35</v>
+        <v>5.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AZ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC6" t="n">
         <v>1.98</v>
       </c>
-      <c r="BA6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.17</v>
-      </c>
       <c r="BD6" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1001,25 +1001,25 @@
         <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="R3" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>3.22</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="X3" t="n">
         <v>2.85</v>
@@ -1028,10 +1028,10 @@
         <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
         <v>1.02</v>
@@ -1043,7 +1043,7 @@
         <v>3.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
         <v>1.77</v>
@@ -1055,22 +1055,22 @@
         <v>1.27</v>
       </c>
       <c r="AI3" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
         <v>1.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,16 +1115,16 @@
         <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.91</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4.88</v>
       </c>
       <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.38</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AR4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV4" t="n">
         <v>2.75</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AW4" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>2.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
         <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,139 +1589,139 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>5.18</v>
+        <v>4.35</v>
       </c>
       <c r="V6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.38</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
         <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AZ6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.21</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC6" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BA4" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BB4" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="V5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.38</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z5" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AU5" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>2.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,139 +1589,139 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="S6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA6" t="n">
         <v>2.9</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="S3" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
@@ -1022,16 +1022,16 @@
         <v>2.62</v>
       </c>
       <c r="X3" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.02</v>
@@ -1046,16 +1046,16 @@
         <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.1</v>
+        <v>6.85</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.06</v>
@@ -1064,7 +1064,7 @@
         <v>1.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
         <v>1.32</v>
@@ -1076,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AT3" t="n">
         <v>2.7</v>
@@ -1094,10 +1094,10 @@
         <v>3.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AX3" t="n">
         <v>1.63</v>
@@ -1106,10 +1106,10 @@
         <v>1.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BB3" t="n">
         <v>1.22</v>
@@ -1118,13 +1118,13 @@
         <v>2.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
         <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.91</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4.82</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.38</v>
+        <v>2.12</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,34 +1392,34 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>3.03</v>
+        <v>3.75</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
         <v>4.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
         <v>2.85</v>
       </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
         <v>7.5</v>
@@ -1428,40 +1428,40 @@
         <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
         <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
         <v>1.92</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
         <v>1.87</v>
@@ -1473,10 +1473,10 @@
         <v>1.32</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AS5" t="n">
         <v>2.38</v>
@@ -1500,7 +1500,7 @@
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BA5" t="n">
         <v>2.65</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="BA6" t="n">
         <v>2.04</v>
       </c>
-      <c r="AT6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="S2" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="T2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="X2" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AF2" t="n">
         <v>2.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AM2" t="n">
         <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -888,10 +888,10 @@
         <v>1.54</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AU2" t="n">
         <v>3.35</v>
@@ -900,34 +900,34 @@
         <v>2.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="BB2" t="n">
         <v>1.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BD2" t="n">
         <v>5.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X3" t="n">
         <v>2.9</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.98</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.85</v>
+        <v>6.65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AM3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP3" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
         <v>2.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>4.82</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.58</v>
+        <v>2.44</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.87</v>
+        <v>2.04</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.48</v>
+        <v>3.28</v>
       </c>
       <c r="T5" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.35</v>
+        <v>3.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AE5" t="n">
         <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.65</v>
+        <v>6.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.05</v>
+        <v>3.48</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.91</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.82</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.5</v>
+        <v>6.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
         <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
         <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.53</v>
+        <v>2.44</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
         <v>3.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="S5" t="n">
-        <v>3.28</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
-        <v>3.28</v>
+        <v>4.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.05</v>
+        <v>6.65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AM5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP5" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
         <v>3.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
         <v>3.45</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI4" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.69</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S2" t="n">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="X2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>2.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AJ2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM2" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.24</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -885,49 +885,49 @@
         <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AS2" t="n">
         <v>1.96</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AU2" t="n">
         <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AZ2" t="n">
         <v>3.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AG3" t="n">
         <v>3.45</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
         <v>1.02</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AN4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1395,25 +1395,25 @@
         <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>4.35</v>
+        <v>3.97</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="X5" t="n">
         <v>2.9</v>
@@ -1434,91 +1434,91 @@
         <v>1.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
         <v>3.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AM5" t="n">
         <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AO5" t="n">
         <v>1.31</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.05</v>
+        <v>3.49</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.65</v>
+        <v>3.27</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
         <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.68</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>1.8</v>
@@ -1589,28 +1589,28 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="S6" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>4.82</v>
+        <v>4.35</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="X6" t="n">
         <v>2.69</v>
@@ -1619,70 +1619,70 @@
         <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.11</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV6" t="n">
         <v>2.73</v>
@@ -1691,31 +1691,31 @@
         <v>2.05</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
         <v>2.87</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -807,7 +807,7 @@
         <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
@@ -888,7 +888,7 @@
         <v>1.91</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AT2" t="n">
         <v>2.8</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="R3" t="n">
-        <v>2.41</v>
+        <v>3.58</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AH3" t="n">
         <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.88</v>
+        <v>3.49</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1198,7 +1198,7 @@
         <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
         <v>2.62</v>
@@ -1219,7 +1219,7 @@
         <v>2.94</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
@@ -1240,10 +1240,10 @@
         <v>3.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
         <v>3.5</v>
@@ -1276,7 +1276,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
         <v>1.79</v>
@@ -1297,13 +1297,13 @@
         <v>1.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AY4" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="BA4" t="n">
         <v>1.96</v>
@@ -1312,13 +1312,13 @@
         <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BD4" t="n">
         <v>3.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BF4" t="n">
         <v>1.14</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN5" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.46</v>
+        <v>2.73</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.27</v>
+        <v>2.87</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>2.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.28</v>
+        <v>2.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AS6" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.87</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -849,7 +849,7 @@
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
@@ -918,7 +918,7 @@
         <v>1.15</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="BD2" t="n">
         <v>4.8</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>2.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.45</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AS5" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.87</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>2.41</v>
+        <v>4.45</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W6" t="n">
         <v>3</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.1</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R5" t="n">
-        <v>2.41</v>
+        <v>4.45</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>2.23</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
         <v>3</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AH5" t="n">
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.1</v>
+        <v>5.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>2.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.45</v>
+        <v>2.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AS6" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.87</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -807,16 +807,16 @@
         <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -843,19 +843,19 @@
         <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" t="n">
         <v>3.45</v>
@@ -870,10 +870,10 @@
         <v>2.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AS2" t="n">
         <v>1.93</v>
@@ -915,19 +915,19 @@
         <v>1.49</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="BC2" t="n">
         <v>1.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
         <v>2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,82 +998,82 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AM3" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>1.22</v>
@@ -1082,55 +1082,55 @@
         <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AY3" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.27</v>
+        <v>1.96</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,118 +1195,118 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="R4" t="n">
-        <v>2.62</v>
+        <v>3.58</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD4" t="n">
         <v>3.2</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO4" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
         <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.96</v>
+        <v>3.27</v>
       </c>
       <c r="BB4" t="n">
         <v>1.25</v>
@@ -1315,19 +1315,19 @@
         <v>2.16</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="BE4" t="n">
         <v>1.64</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1395,25 +1395,25 @@
         <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R5" t="n">
         <v>4.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>4.35</v>
+        <v>4.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="X5" t="n">
         <v>2.69</v>
@@ -1458,19 +1458,19 @@
         <v>1.65</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AM5" t="n">
         <v>1.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.38</v>
@@ -1479,7 +1479,7 @@
         <v>1.72</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AT5" t="n">
         <v>2.7</v>
@@ -1494,7 +1494,7 @@
         <v>2.05</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AY5" t="n">
         <v>1.36</v>
@@ -1509,16 +1509,16 @@
         <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="BD5" t="n">
         <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
         <v>3.45</v>
@@ -1622,19 +1622,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
         <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AF6" t="n">
         <v>1.62</v>
@@ -1652,7 +1652,7 @@
         <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL6" t="n">
         <v>1.94</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -998,70 +998,70 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="R3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="S3" t="n">
         <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
         <v>3.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
         <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD3" t="n">
         <v>3.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.85</v>
+        <v>6.43</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
         <v>1.95</v>
@@ -1079,7 +1079,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR3" t="n">
         <v>1.79</v>
@@ -1097,7 +1097,7 @@
         <v>2.52</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AX3" t="n">
         <v>1.59</v>
@@ -1115,13 +1115,13 @@
         <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
         <v>1.15</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,139 +1195,139 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.31</v>
+        <v>3.85</v>
       </c>
       <c r="R4" t="n">
-        <v>3.58</v>
+        <v>4.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="U4" t="n">
-        <v>4.35</v>
+        <v>4.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.85</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.28</v>
+        <v>2.73</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.85</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>4.78</v>
+        <v>4.35</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="X5" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AH5" t="n">
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.7</v>
+        <v>6.65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -804,19 +804,19 @@
         <v>3.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -831,7 +831,7 @@
         <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.14</v>
@@ -849,7 +849,7 @@
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
@@ -867,13 +867,13 @@
         <v>1.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AX2" t="n">
         <v>1.58</v>
@@ -924,7 +924,7 @@
         <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BF2" t="n">
         <v>1.33</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,130 +998,130 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.19</v>
+        <v>3.85</v>
       </c>
       <c r="R3" t="n">
-        <v>2.64</v>
+        <v>4.45</v>
       </c>
       <c r="S3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD3" t="n">
         <v>3.1</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.43</v>
+        <v>5.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AM3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>1.38</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR3" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="n">
         <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
         <v>1.15</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,130 +1195,130 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="R4" t="n">
-        <v>4.45</v>
+        <v>2.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS4" t="n">
         <v>2.27</v>
       </c>
-      <c r="U4" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AT4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="BB4" t="n">
         <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
         <v>1.15</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.3</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S6" t="n">
         <v>3.45</v>
@@ -1619,7 +1619,7 @@
         <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA6" t="n">
         <v>1.01</v>
@@ -1634,10 +1634,10 @@
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>3.45</v>
@@ -1703,13 +1703,13 @@
         <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
         <v>2.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="BE6" t="n">
         <v>1.57</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>2.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>4.45</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>4.78</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AH3" t="n">
         <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.66</v>
+        <v>3.38</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>3.19</v>
@@ -1261,7 +1261,7 @@
         <v>1.71</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
         <v>1.38</v>
@@ -1449,7 +1449,7 @@
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.1</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>4.45</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.23</v>
-      </c>
       <c r="BD6" t="n">
-        <v>3.38</v>
+        <v>3.66</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -813,28 +813,28 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="X2" t="n">
         <v>2.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
         <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AB2" t="n">
         <v>1.03</v>
@@ -843,37 +843,37 @@
         <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
         <v>3.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
         <v>1.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -885,10 +885,10 @@
         <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AT2" t="n">
         <v>2.8</v>
@@ -900,7 +900,7 @@
         <v>2.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AX2" t="n">
         <v>1.58</v>
@@ -915,16 +915,16 @@
         <v>1.49</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="BF2" t="n">
         <v>1.33</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,130 +1195,130 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.19</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="n">
-        <v>2.64</v>
+        <v>4.45</v>
       </c>
       <c r="S4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
         <v>3.1</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.43</v>
+        <v>5.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AM4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AN4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR4" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="n">
         <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
         <v>1.15</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,130 +1589,130 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>3.19</v>
       </c>
       <c r="R6" t="n">
-        <v>4.45</v>
+        <v>2.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS6" t="n">
         <v>2.27</v>
       </c>
-      <c r="U6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AT6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="BB6" t="n">
         <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
         <v>1.15</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
         <v>3.7</v>
@@ -819,7 +819,7 @@
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
         <v>3.6</v>
@@ -843,19 +843,19 @@
         <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.5</v>
+        <v>5.76</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" t="n">
         <v>3.45</v>
@@ -885,10 +885,10 @@
         <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AT2" t="n">
         <v>2.8</v>
@@ -900,13 +900,13 @@
         <v>2.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>3.1</v>
@@ -1195,31 +1195,31 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
         <v>4.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="U4" t="n">
-        <v>4.78</v>
+        <v>5.19</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
         <v>1.4</v>
@@ -1228,7 +1228,7 @@
         <v>6.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
         <v>1.06</v>
@@ -1246,22 +1246,22 @@
         <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AM4" t="n">
         <v>1.18</v>
@@ -1273,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="S5" t="n">
         <v>2.9</v>
@@ -1407,64 +1407,64 @@
         <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
         <v>3.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
         <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
         <v>3.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
         <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AM5" t="n">
         <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AO5" t="n">
         <v>1.31</v>
@@ -1506,16 +1506,16 @@
         <v>2.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="BF5" t="n">
         <v>1.13</v>
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
         <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.37</v>
+        <v>3.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
         <v>6.43</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.98</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -810,7 +810,7 @@
         <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.5</v>
@@ -822,13 +822,13 @@
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="X2" t="n">
         <v>2.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
         <v>4.5</v>
@@ -840,22 +840,22 @@
         <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.76</v>
+        <v>5.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
         <v>3.45</v>
@@ -864,67 +864,67 @@
         <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AM2" t="n">
         <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="BA2" t="n">
         <v>1.49</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="BF2" t="n">
         <v>1.33</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.75</v>
-      </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM3" t="n">
+      <c r="AU3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.3</v>
       </c>
-      <c r="AU3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.38</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>4.45</v>
+        <v>2.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2.09</v>
       </c>
-      <c r="U4" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.9</v>
+        <v>6.43</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,52 +1276,52 @@
         <v>1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG5" t="n">
         <v>3.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AR5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.24</v>
       </c>
       <c r="BC5" t="n">
         <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BE5" t="n">
         <v>1.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>4.26</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="X6" t="n">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.43</v>
+        <v>5.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG3" t="n">
         <v>3.5</v>
       </c>
-      <c r="R3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS3" t="n">
         <v>2.2</v>
       </c>
-      <c r="U3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AT3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="BC3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3.1</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AU5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="BC5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH5" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="X3" t="n">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AH3" t="n">
         <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>6.43</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AM3" t="n">
         <v>1.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="BC3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,130 +1195,130 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.1</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
         <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.99</v>
+        <v>3.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.43</v>
+        <v>8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
         <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
         <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BF4" t="n">
         <v>1.12</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,139 +1392,139 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3.58</v>
+        <v>4.26</v>
       </c>
       <c r="S5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.9</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
       <c r="X5" t="n">
-        <v>3.33</v>
+        <v>2.82</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
         <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
         <v>2.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,139 +1589,139 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>4.26</v>
+        <v>3.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.9</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.82</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AN6" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
         <v>2.4</v>
@@ -825,31 +825,31 @@
         <v>3.8</v>
       </c>
       <c r="X2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Y2" t="n">
         <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.5</v>
+        <v>6.03</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AG2" t="n">
         <v>2.1</v>
@@ -861,19 +861,19 @@
         <v>3.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AM2" t="n">
         <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -882,52 +882,52 @@
         <v>1.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AS2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AU2" t="n">
         <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AY2" t="n">
         <v>1.45</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,139 +998,139 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="R3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.69</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.8</v>
       </c>
       <c r="X3" t="n">
         <v>2.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.43</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
         <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BF3" t="n">
         <v>1.13</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.07</v>
-      </c>
       <c r="AU4" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AX4" t="n">
         <v>1.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.34</v>
+        <v>1.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>4.26</v>
+        <v>2.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.9</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.82</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.75</v>
+        <v>6.43</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,52 +1473,52 @@
         <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,139 +1589,139 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>4.33</v>
+        <v>3.07</v>
       </c>
       <c r="V6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.33</v>
       </c>
-      <c r="W6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AZ6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
         <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
         <v>46105.69791666666</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>3.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>5.04</v>
+        <v>3.07</v>
       </c>
       <c r="V4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.37</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN4" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
         <v>1.85</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AT4" t="n">
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AY4" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.54</v>
+        <v>4.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>5.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
         <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI5" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,70 +1589,70 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U6" t="n">
         <v>3.1</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.07</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="X6" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AD6" t="n">
         <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.95</v>
+        <v>3.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.8</v>
+        <v>6.43</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
         <v>1.91</v>
@@ -1661,61 +1661,61 @@
         <v>1.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.48</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AS6" t="n">
         <v>2.25</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AX6" t="n">
         <v>1.57</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -994,17 +994,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="R3" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="S3" t="n">
         <v>2.4</v>
@@ -1016,34 +1016,34 @@
         <v>4.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
         <v>7.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>3.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
         <v>1.75</v>
@@ -1052,7 +1052,7 @@
         <v>3.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
         <v>6</v>
@@ -1067,40 +1067,40 @@
         <v>1.87</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AO3" t="n">
         <v>1.31</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.05</v>
+        <v>3.49</v>
       </c>
       <c r="AV3" t="n">
         <v>2.28</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AY3" t="n">
         <v>1.3</v>
@@ -1121,10 +1121,10 @@
         <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>1.8</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>5.04</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
         <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>2.05</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BA5" t="n">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.54</v>
+        <v>4.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>5.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
         <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI6" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.06</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.3</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>3.07</v>
+        <v>5.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AN4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
         <v>1.85</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AT4" t="n">
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AY4" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>3.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>5.04</v>
+        <v>3.07</v>
       </c>
       <c r="V6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.37</v>
       </c>
-      <c r="W6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AD6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN6" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR6" t="n">
         <v>1.85</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AY6" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-24.xlsx
+++ b/jogos_2026-03-24.xlsx
@@ -772,54 +772,54 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="U2" t="n">
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
         <v>3.8</v>
@@ -828,10 +828,10 @@
         <v>2.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.18</v>
@@ -840,34 +840,34 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.03</v>
+        <v>5.45</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AM2" t="n">
         <v>1.25</v>
@@ -882,37 +882,37 @@
         <v>1.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AU2" t="n">
         <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BB2" t="n">
         <v>1.12</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -987,150 +987,150 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="R3" t="n">
-        <v>3.58</v>
+        <v>4.26</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
         <v>1.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
         <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>7.28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>1.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AT3" t="n">
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.49</v>
+        <v>3.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1191,143 +1191,143 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>5.04</v>
+        <v>4.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="AA4" t="n">
         <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AN4" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AT4" t="n">
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>3.49</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BI4" s="3" t="n">
         <v>46105.69791666666</v>
@@ -1363,42 +1363,42 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>3.1</v>
@@ -1416,13 +1416,13 @@
         <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="Y5" t="n">
         <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA5" t="n">
         <v>1.09</v>
@@ -1449,16 +1449,16 @@
         <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
         <v>1.35</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.44</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="AS5" t="n">
         <v>2.25</v>
@@ -1503,7 +1503,7 @@
         <v>2.05</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BB5" t="n">
         <v>1.29</v>
@@ -1563,48 +1563,48 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="V6" t="n">
         <v>1.48</v>
@@ -1613,10 +1613,10 @@
         <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
         <v>9</v>
@@ -1625,43 +1625,43 @@
         <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
         <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AM6" t="n">
         <v>1.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>1.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AR6" t="n">
         <v>1.85</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1691,7 +1691,7 @@
         <v>1.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
         <v>1.33</v>
@@ -1706,7 +1706,7 @@
         <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD6" t="n">
         <v>3.2</v>
@@ -1715,7 +1715,7 @@
         <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
